--- a/docs/dialogue-all-coach.xlsx
+++ b/docs/dialogue-all-coach.xlsx
@@ -10,6 +10,7 @@
     <sheet name="voice割り付け" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="コーチセリフ台帳" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="選手側(招聘)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="voice展開草案" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,12 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -77,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -87,6 +94,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5631,4 +5644,7994 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F249"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>出現箇所</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>データ定数</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>キー</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>voice系統(日本語名)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>セリフ</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>妙に気合の入っとるのがおる。誰とは言わん</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>練習場の空気は悪うない。緩んどる者もおらん</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ここのところ、腰の据わった顔つきが増えとる</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>目の色が変わってきた者が一人いる。名は伏せる</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>練習場の緊張は保たれている。緩みはない</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>足の運びが良くなった者がいる。誰かは言わない</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>全体のフォームのばらつきが、平均してやや小さくなっていますね</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>練習の集中度に、良い傾向が見えるデータがあります</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>一部の選手の反応速度に、伸びの兆候が出ています</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>……誰かの目つきが、変わった</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>……音が、いい。誰の足音かは言わん</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>……たるんどる奴は、今はいない</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>……どなたかの目つきが、変わりました</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>……足音が、良いのです。誰かは申しません</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>……たるんでいる方は、今はいませんよ</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>誰かの表情が、最近柔らかくなってきましたよ</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>あの子かな……まだ誰とは言えませんが、いい変化があります</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>練習場全体の空気が、少し温かくなった気がします</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>誰とは言わないけどよ、目つきが変わった奴がいるんだよ</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>なんかいい空気なんだよなあ、最近の練習場</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>飯の食い方見てりゃわかるもんさ。悪くないよ、今は</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>誰とは言わないけどね、目つきが変わった子がいるのよ</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>なんかいい空気なのよね、最近の練習場</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(E-D級・漠然)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.vague</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>vague</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>飯の食い方見てりゃわかるものよ。悪くないわ、今は</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>{name}、目の光が違うとる。いいぞ</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>{name}は今、乗っとる。この波を逃すな</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>{name}、目の光が違う。悪くない</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>{name}は今、波に乗っている。逃す手はない</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手、練習中の反応がここ数週で明らかに良くなっています</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手、集中の持続時間が延びている傾向が見て取れます</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、いい顔しとる</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、今は乗っとるな</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、いい顔をされています</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、今は乗っていますね</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、最近すごく前向きな顔をしていますよ</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、自分でも手応えを感じ始めているみたいです</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>{name}、最近いい顔して練習に来るんだよなあ</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>{name}、乗ってるよ今。声かけたらもっと伸びるかもな</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>{name}、最近いい顔して練習に来るのよ</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・好調)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_positive</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>named_positive</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>{name}、乗ってるわね今。声かけたらもっと伸びるかもよ</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>{name}、足の踏ん張りが甘い。何かある</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>{name}、目が泳いどる。様子を見ておけ</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>{name}、足の踏ん張りが甘くなっている。何かある</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>{name}、目が泳いでいる。注意しておいた方がいい</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手、練習の集中指標がここ最近やや下がっています</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手、動きの精度に小さなブレが増えてきています</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、少し落ちとる</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、何かある目だ</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、少し落ちていますね</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、何かある目をされています</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、少し元気がないかもしれません。気にかけてあげてください</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、練習中に何か考え込んでいる時間が増えました</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>{name}、なんか元気ないんだよなあ最近。声かけといてやってくれよ</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>{name}、飯の食いっぷりが落ちてる。心配だねえ</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>{name}、なんか元気ないのよね最近。声かけてあげて</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・不調)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_negative</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>named_negative</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>{name}、飯の食いっぷりが落ちてるわ。心配ね</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>{name}は変わらん。変わらんのも力のうちだ</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>{name}、平熱だ。それでいい</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>{name}は変わらない。それも力のひとつ</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>{name}、平熱を保っている。それでいい</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の各種指標は横ばい、安定していると言えますね</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手、特筆すべき変化は観測されていません</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、いつも通りだ</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、変わらん。それでいい</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、いつも通りです</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、変わりません。それでいいのです</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、いつものペースでやっていますよ</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、落ち着いて過ごせているみたいです</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>{name}は相変わらずマイペースだよ、あれはあれでいいんだよ</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>{name}、特に変わりもなく元気にやってるよ</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>{name}は相変わらずマイペースね、あれはあれでいいのよ</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(C級・平常)</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.named_neutral</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>named_neutral</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>{name}、特に変わりもなく元気にやってるわよ</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、確かに上がっとる。追い込んだ甲斐があった</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}が乗ってきた。ここが踏ん張り所だ</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、確かに上がっている。追い込んだ甲斐があった</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}が乗ってきている。ここが踏ん張り所</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、数値上も明確な上昇曲線を描いています</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、直近の測定でも伸びが継続しています</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>……{name}の{stat}、上がっとる。地味だが、確かだ</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、{stat}に手応えがある</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さんの{stat}、上がっています。地味ですが、確かです</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、{stat}に手応えがあります</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>{name}さんの{stat}、着実に伸びてきていますよ。本人も気づいているはずです</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、{stat}が良くなってきています。焦らず続けましょう</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、上がってきてるよ。あの子頑張ってるからなあ</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}に手応え出てきたよ。見てて嬉しくなるね</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、上がってきてるわよ。あの子頑張ってるものね</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・成長中)</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_growing</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>stat_growing</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}に手応え出てきたわ。見てて嬉しくなるわね</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、壁にぶつかっとる。ここからが本番だ</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}が止まった。甘えではない、壁だ</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、壁にぶつかっている。ここからが本番</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}が止まった。甘えではない、壁</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、ここ最近は数値が横ばいで、伸びが鈍化しています</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、成長曲線が一時的にプラトーに入っているようです</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>……{name}の{stat}、止まっとる。焦る段階じゃない</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、{stat}が頭打ちだ。時間がかかる</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さんの{stat}、止まっています。焦る段階ではありません</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、{stat}が頭打ちです。時間がかかりますね</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>{name}さんの{stat}、少し足踏みしていますね。でも悪いことではありませんよ</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、{stat}が伸び悩んでいます。本人も気づいているみたいです</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、ちょっと足踏みしてるなあ。まあこういう時期もあるさ</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}が伸びなくて焦ってるみたいだけど、気長にいこうや</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、ちょっと足踏みしてるわね。まあこういう時期もあるわ</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(B級・停滞)</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.stat_stagnant</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>stat_stagnant</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}が伸びなくて焦ってるみたいだけど、気長にいきましょ</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、天井が見えてきた。ここからは一厘の差だ</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}はもう伸びしろが乏しい。今の形を守れ</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、天井が見えている</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}はもう伸びしろが乏しい。今の形を守るべき</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、成長曲線の傾きから見て、上限にかなり近い水準です</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、これ以上の伸びは統計的にも限定的だと見込まれます</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>……{name}の{stat}、もう天井が近い</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、{stat}は伸びしろが少ない。守りに入る頃合いだ</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さんの{stat}、もう天井が近いです</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、{stat}は伸びしろが少ないです。守りに入る頃合いですね</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>{name}さんの{stat}、もう十分に高いところまで来ていますよ</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、{stat}はこの先はゆっくりになると思います。それも成熟の証です</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、もうだいぶ頭打ち近いなあ。ここまで来たらたいしたもんだよ</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}はこれ以上は厳しいと思うよ。十分やったさ</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、もうだいぶ頭打ち近いわね。ここまで来たらたいしたものよ</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・限界近い)</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.near_cap</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>near_cap</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}はこれ以上は厳しいと思うわ。十分やったわよ</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、まだ底が見えん。追い込めばもっと伸びる</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}には余力がある。今が仕込み時だ</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、まだ底が見えない</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}には余力がある。今が仕込み時</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、成長曲線を見る限り、まだ十分な伸び代が残っています</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>{name}選手の{stat}、上限との差はまだ大きく、投資に見合う数値です</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>……{name}の{stat}、まだ奥がある</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>……{name}、{stat}はまだ伸びる。今は仕込み時だ</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さんの{stat}、まだ奥があります</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>……{name}さん、{stat}はまだ伸びます。今は仕込み時ですね</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>{name}さんの{stat}、まだまだこれからですよ。楽しみです</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>{name}さん、{stat}には十分な余地が残っています。焦らず育てましょう</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、まだまだ伸びるよこれ。楽しみだねえ</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}には余裕あるよ。今のうちにしっかり鍛えとこう</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>{name}の{stat}、まだまだ伸びるわよこれ。楽しみね</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>観察レポート(A級・余地あり)</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>COACH_REPORT_TEXTS.far_from_cap</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>far_from_cap</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>{name}、{stat}には余裕あるわ。今のうちにしっかり鍛えときましょ</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>多分、素直に受け入れるとらん……いや、受け入れるだろう。潮時は本人が一番わかる</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>多分、受け入れる。潮時は本人が一番わかっている</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>本人の様子を見る限り、受容の可能性は高いと見立てています</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>……たぶん、大丈夫だろう</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>……たぶん、大丈夫だと思います</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>本人もそろそろかな、という空気を出していますよ</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>あの子ならすんなり受け入れてくれると思うよ、多分な</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・通る)</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>C_positive</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>あの子ならすんなり受け入れてくれると思うわ、多分ね</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>まだ早いかもしれん。目にまだ光が残っとる</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>まだ早いかもしれない。目にまだ光が残っている</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>現時点のデータからは、時期尚早である可能性が高いと見ています</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>……早い。まだ、やる気だ</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>……早いと思います。まだ、やる気ですから</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>本人はまだやる気みたいですよ。難しいかもしれません</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>いやまだ早いんじゃないかなあ。あの子まだやる気満々だよ</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼C・難)</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>C_negative</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>いやまだ早いんじゃないかしら。あの子まだやる気満々よ</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>本人はもう覚悟を決めとる目だ。通るだろう</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>本人はもう覚悟を決めた目をしている。通るはず</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>練習中の言動から見て、本人の受容度はかなり高いと判断できます</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>……あの目は、もう決めとる</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>……あの目は、もう決めていらっしゃいます</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>本人も覚悟しているようです。大丈夫だと思いますよ</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>本人ももう腹くくってる顔してるよ。大丈夫だろうな</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・通る)</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>B_high</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>本人ももう腹くくってる顔してるわよ。大丈夫だと思うわ</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>正直、五分と見とる。伝え方一つで転ぶぞ</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>正直、五分と見ている。伝え方ひとつで転ぶ</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>正直なところ、受容と拒否は拮抗しています。判断材料が足りません</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>……半々だ。読めん</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>……半々です。読めません</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>正直、気持ちは揺れていると思います。タイミング次第ですね</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>正直五分五分だなあ。あの子の中でも揺れてる感じだよ</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・半々)</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>B_maybe</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>正直五分五分ね。あの子の中でも揺れてる感じよ</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>まだ闘志が消えとらん。断られる覚悟はしておけ</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>まだ闘志が消えていない。断られる覚悟はしておくべき</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>闘争心の指標がまだ高水準です。拒否の可能性が高いと見ています</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>……目が、死んどらん</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>……目が、死んでいらっしゃいません</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>まだ本人には闘志がありますね。断られる覚悟はしてください</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>まだあいつ目が死んでないよ。断られる覚悟はしといた方がいい</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼B・難)</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>B_hard</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>まだあの子目が死んでないわよ。断られる覚悟はしといた方がいいわ</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>間違いない。あれはもう己の中で決着をつけとる</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>間違いない。もう己の中で決着をつけている</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>複数の兆候が揃っています。間違いなく受容すると判断します</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>……間違いない。もう、決めとる</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>……間違いありません。もう、決めていらっしゃいます</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>間違いなく受け入れます。本人もそのつもりですよ</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>間違いないよ。あの子もう次の身の振り方まで考えてるからな</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・確実)</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>A_sure</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>間違いないわ。あの子もう次の身の振り方まで考えてるもの</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>多分、通る。練習終わりの背中に、覚悟が見える</t>
+        </is>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>多分、通る。練習終わりの背中に、覚悟が見える</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>確度は高いと見ます。行動データの傾向が一致しています</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>……たぶん、いい返事が来る</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>……たぶん、いい返事が来ると思います</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>練習後の表情を見ていると……受け入れると思います</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>多分通るんじゃないかなあ。あの子薄々わかってる顔してるよ</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・多分)</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>A_likely</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>多分通るんじゃないかしら。あの子薄々わかってる顔してるわ</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>読めん。あれの中でも、まだ答えが出とらん</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>読めない。まだ本人の中でも答えが出ていない</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>データが矛盾しています。正直、予測は困難です</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>……読めん。闘志と、体が食い違っとる</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>……読めません。闘志と、お身体が食い違っています</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>正直読めないです。本人の中でも揺れてる感じですね</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>読めないんだよなあ、これが。闘志はあるけど体がついてこないみたいでさ</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・不明)</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>A_iffy</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>読めないのよねえ、これが。闘志はあるけど体がついてこないみたいでね</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>やめておけ。あの目はまだ、辞める目じゃない</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>やめておくべき。あの目はまだ、辞める目ではない</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>断言します。現時点での提案は逆効果になる公算が大きいです</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>……よせ。まだ、その時じゃない</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>……おやめください。まだ、その時ではありません</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>止めた方がいい。あの目はまだ引退する目じゃありませんよ</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>やめときな、今は。あの目はまだ辞める目じゃないよ、絶対に</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>引退アドバイス(観察眼A・無理)</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>A_hard</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>やめときなさい、今は。あの目はまだ辞める目じゃないわよ、絶対に</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>「わしを呼んだか。……いいだろう、鍛え直してやる」</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>「甘い顔はせんぞ。それでもいいなら、任せてもらおう」</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>「呼んだか。ならば、鍛え直す」</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>「甘い顔はしない。それでも構わないなら、引き受ける」</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>「お招きいただき光栄です。データに基づいて、着実に成果を出しましょう」</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>「拝見しました、伸びしろのある選手が揃っていますね。楽しみです」</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>「……よろしく頼む」</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>「……手は抜かん」</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>「……よろしくお願いします」</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>「……手は抜きません」</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>「よろしくお願いします。まずは選手一人ひとりを、よく見ることから始めますね」</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>「お力になれるよう、じっくり向き合っていきます」</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>「いやあ、呼んでくれて嬉しいねえ。よろしく頼むよ」</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>「腕が鳴るなあ。みんなでいい汗かこうぜ」</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>「あら、呼んでくれて嬉しいわ。よろしくね」</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>雇用時の挨拶</t>
+        </is>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_HIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>「腕が鳴るわねえ。みんなでいい汗かきましょ」</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>「そうか。……達者でな」</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>「そうか。達者で」</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>「承知しました。短い間でしたが、良いデータが取れました」</t>
+        </is>
+      </c>
+      <c r="F228" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>「……そうか。世話になった」</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>「……そうですか。お世話になりました」</t>
+        </is>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>「そうですか……。選手の皆さんによろしくお伝えください」</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>「そうかい……。世話になったなあ、ありがとよ」</t>
+        </is>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="inlineStr">
+        <is>
+          <t>解雇時の一言</t>
+        </is>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>EVENT_COACH_FIRE_LINES</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>「そう……。お世話になったわね、ありがとう」</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>「よくやった。……あそこまで追い込んだ甲斐があったわい」</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・老師</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>「あれが、鍛えた者の顔だ。文句なしだ」</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>「よくやった。追い込んだ甲斐があった」</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>スパルタ・闘将</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>「あれが、鍛え抜いた者の顔。文句なし」</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>「素晴らしい結果です。積み上げてきた数値が、そのまま結果に出ましたね」</t>
+        </is>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>理論派</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>「あの大舞台での再現性は、本物の実力の証明です」</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>「……いい試合だった」</t>
+        </is>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>職人・無骨</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>「……よく、やった」</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>「……いい試合でした」</t>
+        </is>
+      </c>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>職人・静謐</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>「……よく、やりましたね」</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>「本人が積み重ねてきたものが、ちゃんと実を結びましたね。嬉しいです」</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>見守り型</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>「見ていて、こちらまで胸が熱くなりました」</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>「いやあ最高だったよ！あの舞台であれだけやれるとはなあ」</t>
+        </is>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>人情家・親父</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>「見てて泣きそうになったよ。ほんとよく頑張ったなあ」</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>「もう最高だったわよ！あの舞台であれだけやれるなんてね」</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="5" t="inlineStr">
+        <is>
+          <t>PPVメイン勝利・称賛</t>
+        </is>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>PPV_COACH_PRAISE_LINES</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>人情家・姉御</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>「見てて泣きそうになったわ。ほんとよく頑張ったわね」</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>草案(Sonnet)・レビュー待ち</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/dialogue-all-coach.xlsx
+++ b/docs/dialogue-all-coach.xlsx
@@ -528,1505 +528,1505 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>鬼塚 剛志</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>飛鳥 真琴</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Aerial</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>鶴見 正嗣</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Striker</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>岩田 拓海</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Brawler</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>沢村 玲子</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>朝日 義男</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>紅林 太一</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>白川 沙耶</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>大森 健吾</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Brawler</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>宮本 花菜</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Aerial</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>真壁 龍太</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>長谷川 美咲</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Brawler</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>黒田 修平</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Striker</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>土屋 弘美</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>林 拓海</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Striker</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>森田 悠子</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>篠原 隆</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>赤城 凛</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>西岡 学</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>藤原 千春</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Aerial</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>熊谷 鉄也</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Brawler</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>安藤 美波</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Striker</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>堀内 義孝</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>中村 紗弓</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Aerial</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>宮沢 康弘</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Brawler</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>カルロス 真理</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>大河原 剛士</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>羽田 小百合</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Aerial</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>陳 偉明</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>冴島 楓</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>神崎 鋼子</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>巌流 正道</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Grappler</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>スパルタ</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>葉月 レナ</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Aerial</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>人情家</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>御堂 清四郎</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Submission</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>職人気質</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>如月 薫</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Allround</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
@@ -2087,22 +2087,22 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
@@ -2112,29 +2112,29 @@
           <t>「まだ倒れとらん。見どころはある」</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
@@ -2144,29 +2144,29 @@
           <t>「まだ折れていない。目も死んでいない——見どころはある」</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
@@ -2176,29 +2176,29 @@
           <t>「数値は素直ですよ。フォームの無駄がひとつずつ消えています」</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
@@ -2208,29 +2208,29 @@
           <t>「……手応えは、ある」</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
@@ -2240,29 +2240,29 @@
           <t>「……手応えは、あります」</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
@@ -2272,29 +2272,29 @@
           <t>「あの子、自分で気づき始めましたよ。いい兆しです」</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
@@ -2304,29 +2304,29 @@
           <t>「いやあ、よく食らいついてくるよ。若いってのはいいねえ」</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>招聘・中間報告</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.midterm</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
@@ -2336,29 +2336,29 @@
           <t>「よく食らいついてくるのよ、あの子。若いっていいわね」</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
@@ -2368,29 +2368,29 @@
           <t>「最近、練習に身が入っとらん。あれを甘やかすなら、わしは降りる」</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
@@ -2400,29 +2400,29 @@
           <t>「練習に身が入っていない。あれを甘やかすなら、指導はここまでにする」</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
@@ -2432,29 +2432,29 @@
           <t>「提案したメニューを、彼女は感覚で崩してしまう。これでは計測になりません」</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
@@ -2464,29 +2464,29 @@
           <t>「……合わん。それだけだ」</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
@@ -2496,29 +2496,29 @@
           <t>「……合いませんね。どちらが悪いのでも、ないのですが」</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
@@ -2528,29 +2528,29 @@
           <t>「私の待ち方が、あの子には焦れったいようです。悪いのはどちらでもないのですが」</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
@@ -2560,29 +2560,29 @@
           <t>「近づこうとするほど、あの子は一歩引くんだよ。参ったね」</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>招聘・衝突</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.conflict</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
@@ -2592,29 +2592,29 @@
           <t>「近づこうとするほど、一歩引かれちゃってね。……参ったわ」</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
@@ -2624,29 +2624,29 @@
           <t>「もう2週寄こせ。あれはまだ伸びる」</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
@@ -2656,29 +2656,29 @@
           <t>「あと2週。あの子には、まだ上がある」</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
@@ -2688,29 +2688,29 @@
           <t>「あと2週あれば、いま作りかけの型が完成します。数字で保証しますよ」</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
@@ -2720,29 +2720,29 @@
           <t>「……もう少し、見たい」</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
@@ -2752,29 +2752,29 @@
           <t>「……もう少しだけ、見せてください」</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
@@ -2784,29 +2784,29 @@
           <t>「芽が出る直前なんです。ここで離れるのは、もったいない」</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
@@ -2816,29 +2816,29 @@
           <t>「なあ社長、もうちょっとだけあの子に付き合わせてくれよ」</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>招聘・延長打診</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.extension</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
@@ -2848,29 +2848,29 @@
           <t>「ねえ社長、もう少しだけあの子に付き合わせてくれない？」</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
@@ -2880,29 +2880,29 @@
           <t>「よく耐えた。あれはもう、わしが居らんでも勝手に強くなる」</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
@@ -2912,29 +2912,29 @@
           <t>「よく耐えた。もう、誰かに追い込まれなくても強くなれる」</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
@@ -2944,29 +2944,29 @@
           <t>「教科書に載せたいくらいの吸収曲線でした。データはすべて置いていきます」</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
@@ -2976,29 +2976,29 @@
           <t>「……いいものを見た。あとは、あいつのものだ」</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
@@ -3008,29 +3008,29 @@
           <t>「……いいものを見ました。あとは、あの子のものです」</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
@@ -3040,29 +3040,29 @@
           <t>「私は何も教えていません。あの子が、自分で見つけたんです」</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
@@ -3072,29 +3072,29 @@
           <t>「別れが寂しくなっちまった。いい子を預かったよ、社長」</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果大)</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradGood</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
@@ -3104,29 +3104,29 @@
           <t>「別れが寂しくなっちゃった。いい子を預かったわ、社長」</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>sparta_roshi</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>スパルタ・老師</t>
         </is>
@@ -3136,29 +3136,29 @@
           <t>「土台は作った。ここから先は本人の覚悟の問題だ」</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>sparta_tosho</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>スパルタ・闘将</t>
         </is>
@@ -3168,29 +3168,29 @@
           <t>「土台は作った。ここから先は、本人の覚悟の問題」</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>theorist</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>理論派</t>
         </is>
@@ -3200,29 +3200,29 @@
           <t>「伸び幅は想定の範囲内です。継続すれば、もう一段あります」</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>artisan_bukotsu</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>職人・無骨</t>
         </is>
@@ -3232,29 +3232,29 @@
           <t>「……悪くはない」</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>artisan_seihitsu</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>職人・静謐</t>
         </is>
@@ -3264,29 +3264,29 @@
           <t>「……悪くは、ありません」</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>mentor</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>見守り型</t>
         </is>
@@ -3296,29 +3296,29 @@
           <t>「ゆっくりな子です。でも、蒔いた種は消えませんよ」</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>bigheart_oyaji</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>人情家・親父</t>
         </is>
@@ -3328,29 +3328,29 @@
           <t>「まあ、こんなもんさ。でも あの子、最後まで笑って走ってたよ」</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>招聘・卒業(成果並)</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>COACH_INVITE_LINES.gradNormal</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>bigheart_anego</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>人情家・姉御</t>
         </is>
@@ -3360,29 +3360,29 @@
           <t>「まあ、こんなものよ。でもあの子、最後まで笑って走ってたわよ」</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>招聘・化ける(地の文)</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>INVITE_AWAKENING_LINES.narration</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>(共通)</t>
         </is>
@@ -3392,29 +3392,29 @@
           <t>4週間の最終日——彼女の動きに、来たときとは別人の何かが宿っていた。</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>招聘・化ける(コーチ)</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>INVITE_AWAKENING_LINES.coachLine</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>(共通・中立形)</t>
         </is>
@@ -3424,29 +3424,29 @@
           <t>「……こういう瞬間に立ち会うために、この仕事をしている」</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>観察レポート(E-D級・漠然)</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.vague</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3456,29 +3456,29 @@
           <t>最近、練習に身が入っている選手がいるようです</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>観察レポート(E-D級・漠然)</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.vague</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3488,29 +3488,29 @@
           <t>ちょっと元気のない選手がいますね</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>観察レポート(E-D級・漠然)</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.vague</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3520,29 +3520,29 @@
           <t>練習場の雰囲気は悪くないですよ</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>観察レポート(E-D級・漠然)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.vague</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3552,29 +3552,29 @@
           <t>全体的にまずまずの仕上がりですね</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>観察レポート(E-D級・漠然)</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.vague</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3584,29 +3584,29 @@
           <t>最近、動きが良くなってきた選手がいます</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>観察レポート(E-D級・漠然)</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.vague</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3616,29 +3616,29 @@
           <t>ちょっと伸び悩んでいる選手がいるかもしれません</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・好調)</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_positive</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3648,29 +3648,29 @@
           <t>{name}選手、調子が良さそうですね</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・好調)</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_positive</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3680,29 +3680,29 @@
           <t>{name}選手、最近いい感じに仕上がってきています</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・好調)</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_positive</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3712,29 +3712,29 @@
           <t>{name}選手の動きに勢いを感じます</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・不調)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_negative</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3744,29 +3744,29 @@
           <t>{name}選手、少し調子が落ちているかもしれません</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・不調)</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_negative</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3776,29 +3776,29 @@
           <t>{name}選手、ちょっと練習に集中できていない様子です</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・不調)</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_negative</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3808,29 +3808,29 @@
           <t>{name}選手、最近少し元気がないですね</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・平常)</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_neutral</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3840,29 +3840,29 @@
           <t>{name}選手は安定していますよ</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・平常)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_neutral</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3872,29 +3872,29 @@
           <t>{name}選手、特に問題はないようです</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>観察レポート(C級・平常)</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.named_neutral</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3904,29 +3904,29 @@
           <t>{name}選手はマイペースにやっています</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>観察レポート(B級・成長中)</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.stat_growing</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3936,29 +3936,29 @@
           <t>{name}選手の{stat}が伸びてきています</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>観察レポート(B級・成長中)</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.stat_growing</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -3968,29 +3968,29 @@
           <t>{name}選手、{stat}の成長が見られますね</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>観察レポート(B級・成長中)</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.stat_growing</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4000,29 +4000,29 @@
           <t>{name}選手の{stat}に手応えを感じます</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>観察レポート(B級・停滞)</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.stat_stagnant</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4032,29 +4032,29 @@
           <t>{name}選手の{stat}、最近伸びが止まっている気がします</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>観察レポート(B級・停滞)</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.stat_stagnant</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4064,29 +4064,29 @@
           <t>{name}選手、{stat}はちょっと頭打ち気味ですかね</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>観察レポート(B級・停滞)</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.stat_stagnant</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4096,29 +4096,29 @@
           <t>{name}選手の{stat}、ここから先は時間がかかるかもしれません</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>観察レポート(A級・限界近い)</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.near_cap</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4128,29 +4128,29 @@
           <t>{name}選手の{stat}、そろそろ頭打ちかもしれません</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>観察レポート(A級・限界近い)</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.near_cap</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4160,29 +4160,29 @@
           <t>{name}選手の{stat}はもう伸びしろが少ないと思います</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>観察レポート(A級・限界近い)</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.near_cap</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4192,29 +4192,29 @@
           <t>{name}選手の{stat}、限界に近づいている気がします</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>観察レポート(A級・余地あり)</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.far_from_cap</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4224,29 +4224,29 @@
           <t>{name}選手の{stat}、まだまだ伸びますよ</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>観察レポート(A級・余地あり)</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.far_from_cap</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4256,29 +4256,29 @@
           <t>{name}選手の{stat}にはまだ余力がありますね</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>観察レポート(A級・余地あり)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>COACH_REPORT_TEXTS.far_from_cap</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4288,29 +4288,29 @@
           <t>{name}選手の{stat}の成長余地は十分です</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>雇用時の挨拶</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_HIRE_LINES</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4320,29 +4320,29 @@
           <t>一緒に頑張りましょう！期待してください。</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>雇用時の挨拶</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_HIRE_LINES</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4352,29 +4352,29 @@
           <t>お任せください。選手たちを鍛え上げてみせます！</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>雇用時の挨拶</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_HIRE_LINES</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4384,29 +4384,29 @@
           <t>この団体で働けて光栄です。全力でサポートします。</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>雇用時の挨拶</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_HIRE_LINES</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4416,29 +4416,29 @@
           <t>腕が鳴りますね…。素晴らしい選手たちだ。</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>解雇時の一言</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_FIRE_LINES</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4448,29 +4448,29 @@
           <t>そうですか…。今までありがとうございました。</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>解雇時の一言</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_FIRE_LINES</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4480,29 +4480,29 @@
           <t>お世話になりました。選手たちによろしくお伝えください。</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>解雇時の一言</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>EVENT_COACH_FIRE_LINES</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4512,29 +4512,29 @@
           <t>残念ですが…また機会があれば。</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4544,29 +4544,29 @@
           <t>この選手は本当に素晴らしい。日頃の努力が、最高の舞台で実を結びました</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4576,29 +4576,29 @@
           <t>見事です。あの大舞台で、持てる力を全て出し切りました</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4608,29 +4608,29 @@
           <t>よくやってくれました。この勝利は、本人の努力の結晶です</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4640,29 +4640,29 @@
           <t>素晴らしい試合でした。これだけの選手を指導できて光栄です</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4672,29 +4672,29 @@
           <t>あの舞台で勝てる選手は限られています。本当に立派でした</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4704,29 +4704,29 @@
           <t>成長を間近で見てきましたが、ここまでの選手になるとは……脱帽です</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4736,29 +4736,29 @@
           <t>日頃の練習がそのままリングに出ていました。コーチ冥利に尽きます</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>PPVメイン勝利・称賛</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>PPV_COACH_PRAISE_LINES</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4768,29 +4768,29 @@
           <t>この勝利は偶然ではありません。積み重ねてきたものが違います</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase B で voice 展開予定</t>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼C・通る)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4800,29 +4800,29 @@
           <t>多分、受け入れてくれると思いますよ</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼C・通る)</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.C_positive</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4832,29 +4832,29 @@
           <t>本人もそろそろかなって感じはありますね</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼C・難)</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4864,29 +4864,29 @@
           <t>うーん…まだ早いかもしれませんね</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼C・難)</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.C_negative</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4896,29 +4896,29 @@
           <t>本人はまだやる気ですよ。難しいかと</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼B・通る)</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4928,29 +4928,29 @@
           <t>本人も覚悟しているようです。通ると思いますよ</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼B・通る)</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.B_high</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4960,29 +4960,29 @@
           <t>体の衰えは本人が一番わかってますから。大丈夫でしょう</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼B・半々)</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -4992,29 +4992,29 @@
           <t>正直、半々ですね。受け入れるかどうかは本人次第です</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼B・半々)</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.B_maybe</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5024,29 +5024,29 @@
           <t>気持ちは揺れてると思います。タイミング次第かと</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼B・難)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5056,29 +5056,29 @@
           <t>まだ本人には闘志がありますね。断られる覚悟はしてください</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼B・難)</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.B_hard</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5088,29 +5088,29 @@
           <t>目が死んでないですよ、あの選手。引退は早いかと</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・確実)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5120,29 +5120,29 @@
           <t>間違いなく受け入れます。本人もそのつもりです</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・確実)</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_sure</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5152,29 +5152,29 @@
           <t>あの選手、次の身の振り方まで考え始めてますよ</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・多分)</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5184,29 +5184,29 @@
           <t>多分通るでしょう。本人も薄々わかってますから</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・多分)</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_likely</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5216,29 +5216,29 @@
           <t>練習後の表情を見ていると…受け入れると思います</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・不明)</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5248,29 +5248,29 @@
           <t>正直読めないです。本人の中でも揺れてる感じですね</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・不明)</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_iffy</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5280,29 +5280,29 @@
           <t>闘志はあるけど体がついてこない…複雑な状態です</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・無理)</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5312,29 +5312,29 @@
           <t>止めた方がいい。あの目はまだ引退する目じゃない</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>引退アドバイス(観察眼A・無理)</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>COACH_RETIRE_ADVICE_TEXTS.A_hard</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>(全コーチ共通)</t>
         </is>
@@ -5344,9 +5344,9 @@
           <t>断言しますが、今は無理です。怒らせるだけですよ</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>現行共通口調 → Phase A で voice 展開予定</t>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>voice版に置き換え済み・coach-lines.js内は削除</t>
         </is>
       </c>
     </row>
@@ -5399,17 +5399,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
@@ -5419,24 +5419,24 @@
           <t>「自分の身体が変わっていくのが、毎日わかったんです」</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>お嬢様</t>
         </is>
@@ -5446,24 +5446,24 @@
           <t>「よい師でしたわ。……少しだけ、涙が出ましたけれど」</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>不良</t>
         </is>
@@ -5473,24 +5473,24 @@
           <t>「べつに。……まあ、アイツの言うことは全部正しかったけどな」</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>クール</t>
         </is>
@@ -5500,24 +5500,24 @@
           <t>「収穫はあった。それ以上でも以下でもない」</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>妖艶</t>
         </is>
@@ -5527,24 +5527,24 @@
           <t>「あんなに汗をかいたの、いつ以来かしら。悪くない4週間だったわ」</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>礼儀正しい</t>
         </is>
@@ -5554,24 +5554,24 @@
           <t>「最後の日、深く頭を下げました。それしかできることがなくて」</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(手応えあり)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_LINES</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>鷹揚</t>
         </is>
@@ -5581,24 +5581,24 @@
           <t>「いい時間だったよ。ああいう出会いは、キャリアにそう何度もない」</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(並・共通)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_NORMAL_LINES</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>(共通)</t>
         </is>
@@ -5608,24 +5608,24 @@
           <t>「……正直、まだ消化しきれてません。でも無駄じゃなかったと思います」</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>卒業・選手の一言(並・共通)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>FIGHTER_INVITE_GRAD_NORMAL_LINES</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>(共通)</t>
         </is>
@@ -5635,7 +5635,7 @@
           <t>「合ってたのかどうかは、次の試合で確かめます」</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>確定・voice対応済(2026-07-07)</t>
         </is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8347,7 +8347,7 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9307,7 +9307,7 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10139,7 +10139,7 @@
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10171,7 @@
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10267,7 +10267,7 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11035,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11195,7 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11419,7 +11419,7 @@
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11963,7 @@
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12091,7 +12091,7 @@
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12219,7 +12219,7 @@
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12315,7 +12315,7 @@
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12347,7 +12347,7 @@
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13147,7 +13147,7 @@
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13403,7 +13403,7 @@
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13627,7 @@
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>草案(Sonnet)・レビュー待ち</t>
+          <t>実装済み(2026-07-08)</t>
         </is>
       </c>
     </row>
